--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1569,6 +1569,879 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127862424</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91792</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rörmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>408519</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6754471</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127862432</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75127</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rörmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>408339</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6754417</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127862428</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rörmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>408217</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6754415</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127862434</v>
+      </c>
+      <c r="B13" t="n">
+        <v>82861</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rörmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>408344</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6754416</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127862436</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91634</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rörmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>408344</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6754416</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127862430</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rörmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>408307</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6754458</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127862440</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91303</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rörmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>408325</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6754463</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127862438</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rörmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>408457</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6754422</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127862426</v>
+      </c>
+      <c r="B18" t="n">
+        <v>75144</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rörmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>408182</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6754395</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>127862424</v>
       </c>
       <c r="B10" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>127862432</v>
       </c>
       <c r="B11" t="n">
-        <v>75127</v>
+        <v>75130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>127862428</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127862434</v>
       </c>
       <c r="B13" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127862436</v>
       </c>
       <c r="B14" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>127862430</v>
       </c>
       <c r="B15" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>127862440</v>
       </c>
       <c r="B16" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>127862438</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>127862426</v>
       </c>
       <c r="B18" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>127862424</v>
       </c>
       <c r="B10" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>127862432</v>
       </c>
       <c r="B11" t="n">
-        <v>75130</v>
+        <v>75136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>127862428</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127862434</v>
       </c>
       <c r="B13" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127862436</v>
       </c>
       <c r="B14" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>127862430</v>
       </c>
       <c r="B15" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>127862440</v>
       </c>
       <c r="B16" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>127862438</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>127862426</v>
       </c>
       <c r="B18" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>127862424</v>
       </c>
       <c r="B10" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127862436</v>
       </c>
       <c r="B14" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>127862430</v>
       </c>
       <c r="B15" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>127862440</v>
       </c>
       <c r="B16" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>127862424</v>
       </c>
       <c r="B10" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127862436</v>
       </c>
       <c r="B14" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>127862430</v>
       </c>
       <c r="B15" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>127862440</v>
       </c>
       <c r="B16" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>127862424</v>
       </c>
       <c r="B10" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127862436</v>
       </c>
       <c r="B14" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>127862430</v>
       </c>
       <c r="B15" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>127862440</v>
       </c>
       <c r="B16" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127862432</v>
+        <v>127862428</v>
       </c>
       <c r="B11" t="n">
-        <v>75136</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408339</v>
+        <v>408217</v>
       </c>
       <c r="R11" t="n">
-        <v>6754417</v>
+        <v>6754415</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,32 +1765,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127862428</v>
+        <v>127862432</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>75136</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408217</v>
+        <v>408339</v>
       </c>
       <c r="R12" t="n">
-        <v>6754415</v>
+        <v>6754417</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>127862424</v>
       </c>
       <c r="B10" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127862428</v>
+        <v>127862432</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>75139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408217</v>
+        <v>408339</v>
       </c>
       <c r="R11" t="n">
-        <v>6754415</v>
+        <v>6754417</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,32 +1765,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127862432</v>
+        <v>127862428</v>
       </c>
       <c r="B12" t="n">
-        <v>75136</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408339</v>
+        <v>408217</v>
       </c>
       <c r="R12" t="n">
-        <v>6754417</v>
+        <v>6754415</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1865,7 +1865,7 @@
         <v>127862434</v>
       </c>
       <c r="B13" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127862436</v>
       </c>
       <c r="B14" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>127862430</v>
       </c>
       <c r="B15" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>127862440</v>
       </c>
       <c r="B16" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>127862438</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>127862426</v>
       </c>
       <c r="B18" t="n">
-        <v>75153</v>
+        <v>75156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>127862424</v>
       </c>
       <c r="B10" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127862432</v>
+        <v>127862428</v>
       </c>
       <c r="B11" t="n">
-        <v>75139</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408339</v>
+        <v>408217</v>
       </c>
       <c r="R11" t="n">
-        <v>6754417</v>
+        <v>6754415</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,32 +1765,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127862428</v>
+        <v>127862432</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>75154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408217</v>
+        <v>408339</v>
       </c>
       <c r="R12" t="n">
-        <v>6754415</v>
+        <v>6754417</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1865,7 +1865,7 @@
         <v>127862434</v>
       </c>
       <c r="B13" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127862436</v>
       </c>
       <c r="B14" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>127862430</v>
       </c>
       <c r="B15" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>127862440</v>
       </c>
       <c r="B16" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>127862438</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>127862426</v>
       </c>
       <c r="B18" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127862428</v>
+        <v>127862432</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>75154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408217</v>
+        <v>408339</v>
       </c>
       <c r="R11" t="n">
-        <v>6754415</v>
+        <v>6754417</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,32 +1765,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127862432</v>
+        <v>127862428</v>
       </c>
       <c r="B12" t="n">
-        <v>75154</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408339</v>
+        <v>408217</v>
       </c>
       <c r="R12" t="n">
-        <v>6754417</v>
+        <v>6754415</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>127862424</v>
       </c>
       <c r="B10" t="n">
-        <v>91906</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>127862432</v>
       </c>
       <c r="B11" t="n">
-        <v>75154</v>
+        <v>75158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>127862428</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127862434</v>
       </c>
       <c r="B13" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127862436</v>
       </c>
       <c r="B14" t="n">
-        <v>91748</v>
+        <v>91760</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>127862430</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>127862440</v>
       </c>
       <c r="B16" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>127862438</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>127862426</v>
       </c>
       <c r="B18" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69623260</v>
+        <v>69623294</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408346.0556100241</v>
+        <v>408349</v>
       </c>
       <c r="R2" t="n">
-        <v>6754507.106769001</v>
+        <v>6754419</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2017-08-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69623257</v>
+        <v>127862436</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408406.7985880129</v>
+        <v>408344</v>
       </c>
       <c r="R3" t="n">
-        <v>6754500.188331109</v>
+        <v>6754416</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69623292</v>
+        <v>69623260</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408341.9921756144</v>
+        <v>408346</v>
       </c>
       <c r="R4" t="n">
-        <v>6754462.93109265</v>
+        <v>6754507</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2017-08-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69623297</v>
+        <v>69623295</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408453.962782492</v>
+        <v>408349</v>
       </c>
       <c r="R5" t="n">
-        <v>6754439.121436186</v>
+        <v>6754419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2017-08-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69623294</v>
+        <v>127862424</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408349.1435466707</v>
+        <v>408519</v>
       </c>
       <c r="R6" t="n">
-        <v>6754418.952276326</v>
+        <v>6754471</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,49 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69623291</v>
+        <v>127862434</v>
       </c>
       <c r="B7" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408216.7739942604</v>
+        <v>408344</v>
       </c>
       <c r="R7" t="n">
-        <v>6754407.769717714</v>
+        <v>6754416</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,49 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69623295</v>
+        <v>127862440</v>
       </c>
       <c r="B8" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408349.1435466707</v>
+        <v>408325</v>
       </c>
       <c r="R8" t="n">
-        <v>6754418.952276326</v>
+        <v>6754463</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1462,16 +1357,11 @@
         <v>69623290</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408216.7739942604</v>
+        <v>408217</v>
       </c>
       <c r="R9" t="n">
-        <v>6754407.769717714</v>
+        <v>6754408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2017-08-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127862424</v>
+        <v>69623297</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408519</v>
+        <v>408454</v>
       </c>
       <c r="R10" t="n">
-        <v>6754471</v>
+        <v>6754439</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,44 +1536,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127862432</v>
+        <v>127862428</v>
       </c>
       <c r="B11" t="n">
-        <v>75158</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408339</v>
+        <v>408217</v>
       </c>
       <c r="R11" t="n">
-        <v>6754417</v>
+        <v>6754415</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,14 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127862428</v>
+        <v>127862438</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1800,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408217</v>
+        <v>408457</v>
       </c>
       <c r="R12" t="n">
-        <v>6754415</v>
+        <v>6754422</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1862,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127862434</v>
+        <v>127862432</v>
       </c>
       <c r="B13" t="n">
-        <v>82946</v>
+        <v>83290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408344</v>
+        <v>408339</v>
       </c>
       <c r="R13" t="n">
-        <v>6754416</v>
+        <v>6754417</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1959,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127862436</v>
+        <v>127862426</v>
       </c>
       <c r="B14" t="n">
-        <v>91760</v>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408344</v>
+        <v>408182</v>
       </c>
       <c r="R14" t="n">
-        <v>6754416</v>
+        <v>6754395</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2056,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127862430</v>
+        <v>69623292</v>
       </c>
       <c r="B15" t="n">
-        <v>91482</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408307</v>
+        <v>408342</v>
       </c>
       <c r="R15" t="n">
-        <v>6754458</v>
+        <v>6754463</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2121,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,22 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127862440</v>
+        <v>69623291</v>
       </c>
       <c r="B16" t="n">
-        <v>91429</v>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408325</v>
+        <v>408217</v>
       </c>
       <c r="R16" t="n">
-        <v>6754463</v>
+        <v>6754408</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2218,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2238,209 +2118,15 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>127862438</v>
-      </c>
-      <c r="B17" t="n">
-        <v>79087</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Rörmyran, Dlr</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>408457</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6754422</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Malung-Sälen</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Lima</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Olov Tranberg</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Olov Tranberg</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>127862426</v>
-      </c>
-      <c r="B18" t="n">
-        <v>75175</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Rörmyran, Dlr</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>408182</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6754395</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Malung-Sälen</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Lima</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Olov Tranberg</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Olov Tranberg</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26616-2024 artfynd.xlsx
+++ b/artfynd/A 26616-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69623294</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862436</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69623260</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69623295</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862424</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862434</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862440</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69623290</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69623297</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862428</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862438</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862432</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862426</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69623292</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,8 +2202,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69623291</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>